--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484278_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484278_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9884</v>
+        <v>9.536899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1103</v>
+        <v>4.4136</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8781</v>
+        <v>5.1233</v>
       </c>
       <c r="G2" t="n">
         <v>5.896</v>
@@ -610,13 +610,13 @@
         <v>3.5162</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.2373</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0756</v>
+        <v>-0.7723</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2899</v>
+        <v>0.535</v>
       </c>
       <c r="V2" t="n">
         <v>2.3154</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.2615</v>
+        <v>7.7136</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5758</v>
+        <v>4.1913</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6857</v>
+        <v>3.5223</v>
       </c>
       <c r="G3" t="n">
         <v>3.4774</v>
@@ -688,13 +688,13 @@
         <v>2.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2447</v>
+        <v>0.6967</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1282</v>
+        <v>0.7437</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1165</v>
+        <v>-0.047</v>
       </c>
       <c r="V3" t="n">
         <v>0.6093</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2685</v>
+        <v>5.3221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0504</v>
+        <v>2.4081</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2181</v>
+        <v>2.9139</v>
       </c>
       <c r="G4" t="n">
-        <v>2.378</v>
+        <v>2.0917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3275</v>
+        <v>-0.2287</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0505</v>
+        <v>2.3204</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6535</v>
+        <v>2.056</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4119</v>
+        <v>0.6792</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2416</v>
+        <v>1.3768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7245</v>
+        <v>0.0357</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0844</v>
+        <v>-0.9079</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8089</v>
+        <v>0.9435</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9301</v>
+        <v>3.1255</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8785</v>
+        <v>-0.0151</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0964</v>
+        <v>0.1102</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7821</v>
+        <v>-0.1253</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9414</v>
+        <v>1.0968</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2186</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8314</v>
+        <v>4.8804</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4166</v>
+        <v>3.0461</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4148</v>
+        <v>1.8343</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4164</v>
+        <v>3.9519</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7322</v>
+        <v>1.3615</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6842</v>
+        <v>2.5904</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8086</v>
+        <v>3.1527</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7982</v>
+        <v>1.3712</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0105</v>
+        <v>1.7815</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6077</v>
+        <v>0.7992</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9340000000000001</v>
+        <v>-0.0097</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6737</v>
+        <v>0.8089</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9301</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2845</v>
+        <v>0.4244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5614</v>
+        <v>-0.1065</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8459</v>
+        <v>0.5309</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3592</v>
+        <v>4.6859</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7428</v>
+        <v>0.9715</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6164</v>
+        <v>3.7144</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9519</v>
+        <v>4.4164</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3615</v>
+        <v>1.7322</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5904</v>
+        <v>2.6842</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1527</v>
+        <v>2.8086</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3712</v>
+        <v>0.7982</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7815</v>
+        <v>2.0105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7992</v>
+        <v>1.6077</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0097</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8089</v>
+        <v>0.6737</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0968</v>
+        <v>-0.4299</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4099</v>
+        <v>0.1164</v>
       </c>
       <c r="U6" t="n">
-        <v>0.313</v>
+        <v>-0.5463</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.3488</v>
+        <v>4.5937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6031</v>
+        <v>1.1109</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7457</v>
+        <v>3.4828</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3661</v>
+        <v>2.378</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2484</v>
+        <v>0.3275</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1176</v>
+        <v>2.0505</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2923</v>
+        <v>1.6535</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9836</v>
+        <v>0.4119</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3087</v>
+        <v>1.2416</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0737</v>
+        <v>0.7245</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2648</v>
+        <v>-0.0844</v>
       </c>
       <c r="O7" t="n">
         <v>0.8089</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1781</v>
+        <v>1.2037</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2642</v>
+        <v>0.1569</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9139</v>
+        <v>1.0467</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2559</v>
+        <v>3.9638</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4781</v>
+        <v>0.2998</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7778</v>
+        <v>3.664</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0917</v>
+        <v>3.3661</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2287</v>
+        <v>1.2484</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3204</v>
+        <v>2.1176</v>
       </c>
       <c r="J8" t="n">
-        <v>2.056</v>
+        <v>2.2923</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6792</v>
+        <v>0.9836</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3768</v>
+        <v>1.3087</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0357</v>
+        <v>1.0737</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9079</v>
+        <v>0.2648</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9435</v>
+        <v>0.8089</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1255</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0813</v>
+        <v>0.7931</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8198</v>
+        <v>-0.0391</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2615</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0968</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9169</v>
+        <v>0.6219</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4729</v>
+        <v>-0.9586</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3898</v>
+        <v>1.5805</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4893</v>
@@ -1156,13 +1156,13 @@
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.196</v>
+        <v>-0.099</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1888</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9928</v>
+        <v>-0.8021</v>
       </c>
       <c r="V9" t="n">
         <v>0.8195</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0357</v>
+        <v>0.2616</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1232</v>
+        <v>-1.5977</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1589</v>
+        <v>1.8593</v>
       </c>
       <c r="G10" t="n">
         <v>0.4761</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1688</v>
+        <v>0.3948</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1432</v>
+        <v>0.6687</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0257</v>
+        <v>-0.2739</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2097</v>
+        <v>-0.0541</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3533</v>
+        <v>0.4544</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.8386</v>
@@ -1312,13 +1312,13 @@
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2706</v>
+        <v>-1.115</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6048</v>
+        <v>-0.5503</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9498</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8396</v>
+        <v>-1.7034</v>
       </c>
       <c r="E12" t="n">
         <v>-1.2909</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5487</v>
+        <v>-0.4125</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0535</v>
@@ -1390,13 +1390,13 @@
         <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8446</v>
+        <v>-0.7084</v>
       </c>
       <c r="T12" t="n">
         <v>-0.7262999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1183</v>
+        <v>0.0178</v>
       </c>
       <c r="V12" t="n">
         <v>-1.895</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>39.21700000000001</v>
+        <v>39.8224</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4434</v>
+        <v>13.0485</v>
       </c>
       <c r="F13" t="n">
-        <v>26.7736</v>
+        <v>26.7737</v>
       </c>
       <c r="G13" t="n">
         <v>26.3494</v>
@@ -1450,7 +1450,7 @@
         <v>8.1021</v>
       </c>
       <c r="M13" t="n">
-        <v>6.544899999999999</v>
+        <v>6.5449</v>
       </c>
       <c r="N13" t="n">
         <v>-0.8684000000000001</v>
@@ -1468,19 +1468,19 @@
         <v>26.3712</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3025</v>
+        <v>0.9080000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3150999999999995</v>
+        <v>0.2902</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6178000000000002</v>
+        <v>0.6177000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1089</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6513</v>
+        <v>5.651299999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-6.760299999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1269</v>
+        <v>0.1883</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1955</v>
+        <v>0.478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.2897</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2186</v>
+        <v>-0.9885</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9486</v>
+        <v>-2.2149</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.27</v>
+        <v>1.2264</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3249</v>
+        <v>0.3246</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3492</v>
+        <v>-0.3633</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6741</v>
+        <v>0.6879</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8937</v>
+        <v>-1.3131</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2978</v>
+        <v>-1.8516</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4041</v>
+        <v>0.5385</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5057</v>
+        <v>-0.1905</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1294</v>
+        <v>-0.2606</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3763</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2445</v>
+        <v>-0.2221</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4224</v>
+        <v>-1.3706</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1779</v>
+        <v>1.1485</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4273</v>
+        <v>0.7017</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1975</v>
+        <v>0.1228</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2298</v>
+        <v>0.579</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1223</v>
+        <v>1.0663</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0819</v>
+        <v>1.0258</v>
       </c>
       <c r="L15" t="n">
         <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5496</v>
+        <v>-0.3645</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2793</v>
+        <v>-0.903</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2702</v>
+        <v>0.5385</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1261</v>
+        <v>0.0529</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5447</v>
+        <v>-0.4835</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4186</v>
+        <v>0.5364</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4636</v>
+        <v>-0.2602</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.2201</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.4273</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.1975</v>
+      </c>
+      <c r="I16" t="n">
         <v>-0.2298</v>
       </c>
-      <c r="F16" t="n">
-        <v>-0.2339</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.9885</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-2.2149</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.2264</v>
-      </c>
       <c r="J16" t="n">
-        <v>0.3246</v>
+        <v>0.1223</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3633</v>
+        <v>0.0819</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6879</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3131</v>
+        <v>-0.5496</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8516</v>
+        <v>-0.2793</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5385</v>
+        <v>-0.2702</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8425</v>
+        <v>-0.1417</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9684</v>
+        <v>-0.3425</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1258</v>
+        <v>0.2008</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7692</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6739</v>
+        <v>-0.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9048</v>
+        <v>0.0128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7017</v>
+        <v>-1.2186</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1228</v>
+        <v>-0.9486</v>
       </c>
       <c r="I17" t="n">
-        <v>0.579</v>
+        <v>-0.27</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0663</v>
+        <v>-0.3249</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0258</v>
+        <v>0.3492</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3645</v>
+        <v>-0.8937</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.903</v>
+        <v>-1.2978</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5385</v>
+        <v>0.4041</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4942</v>
+        <v>0.0454</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.2751</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2926</v>
+        <v>0.3205</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7429</v>
+        <v>-2.8182</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4053</v>
+        <v>-2.5064</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3377</v>
+        <v>-0.3118</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6288</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.23</v>
+        <v>0.1548</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2504</v>
+        <v>0.1493</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0205</v>
+        <v>0.0054</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3052</v>
+        <v>-3.8309</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2515</v>
+        <v>-2.5643</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0538</v>
+        <v>-1.2666</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2005</v>
+        <v>-4.2521</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3118</v>
+        <v>-2.0934</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8887</v>
+        <v>-2.1587</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5718</v>
+        <v>-1.3252</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1023</v>
+        <v>-0.6511</v>
       </c>
       <c r="L19" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6287</v>
+        <v>-2.9269</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-1.4423</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>-1.4846</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2394</v>
+        <v>-0.4924</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2504</v>
+        <v>-0.3946</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0111</v>
+        <v>-0.0978</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4131</v>
+        <v>-4.0679</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7666</v>
+        <v>-3.1504</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6465</v>
+        <v>-0.9176</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2521</v>
+        <v>-2.2005</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0934</v>
+        <v>-0.3118</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1587</v>
+        <v>-1.8887</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3252</v>
+        <v>-0.5718</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6511</v>
+        <v>0.1023</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9269</v>
+        <v>-1.6287</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4423</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4846</v>
+        <v>-1.2146</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0746</v>
+        <v>0.4767</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5969</v>
+        <v>0.3516</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4777</v>
+        <v>0.1251</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5422</v>
+        <v>-4.6562</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8638</v>
+        <v>-3.1671</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6784</v>
+        <v>-1.4891</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6431</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.859</v>
+        <v>0.745</v>
       </c>
       <c r="T21" t="n">
-        <v>1.175</v>
+        <v>0.8716</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.316</v>
+        <v>-0.1267</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2094</v>
+        <v>-5.2963</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.873</v>
+        <v>-3.1763</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3365</v>
+        <v>-2.12</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5039</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1893</v>
+        <v>0.1025</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2337</v>
+        <v>-0.5371</v>
       </c>
       <c r="U22" t="n">
-        <v>0.423</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9414</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.0594</v>
+        <v>-7.6275</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8082</v>
+        <v>-6.677</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.2512</v>
+        <v>-0.9505</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.4759</v>
+        <v>-5.7124</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6833</v>
+        <v>-0.6956</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7925</v>
+        <v>-5.0168</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8795</v>
+        <v>-2.031</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2459</v>
+        <v>0.8262</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.8573</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5964</v>
+        <v>-3.6813</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4375</v>
+        <v>-1.5219</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1589</v>
+        <v>-2.1595</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-6.0556</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-8.009</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8267</v>
+        <v>0.0977</v>
       </c>
       <c r="T23" t="n">
-        <v>1.607</v>
+        <v>-0.2928</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7803</v>
+        <v>0.3905</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8242</v>
+        <v>4.0428</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3869</v>
+        <v>3.6559</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.340400000000001</v>
+        <v>-8.6906</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2837</v>
+        <v>-3.8194</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0567</v>
+        <v>-4.8713</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.7124</v>
+        <v>-5.4759</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6956</v>
+        <v>-2.6833</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.0168</v>
+        <v>-2.7925</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.031</v>
+        <v>-1.8795</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8262</v>
+        <v>-1.2459</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.8573</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.6813</v>
+        <v>-3.5964</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5219</v>
+        <v>-1.4375</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1595</v>
+        <v>-2.1589</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.0556</v>
+        <v>-0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8.009</v>
+        <v>-2.1488</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6152</v>
+        <v>0.1954</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8995</v>
+        <v>0.5958</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2842</v>
+        <v>-0.4004</v>
       </c>
       <c r="V24" t="n">
-        <v>4.0428</v>
+        <v>-2.8242</v>
       </c>
       <c r="W24" t="n">
-        <v>3.6559</v>
+        <v>-0.3869</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3869</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-39.2168</v>
+        <v>-37.8688</v>
       </c>
       <c r="E25" t="n">
-        <v>-26.7737</v>
+        <v>-26.7736</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.4434</v>
+        <v>-11.0953</v>
       </c>
       <c r="G25" t="n">
         <v>-26.3494</v>
@@ -2383,7 +2383,7 @@
         <v>0.8682000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-7.4131</v>
+        <v>-7.413100000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-19.8044</v>
@@ -2404,13 +2404,13 @@
         <v>12.6971</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3024999999999999</v>
+        <v>1.0458</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6178000000000001</v>
+        <v>-0.6179</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3149</v>
+        <v>1.6634</v>
       </c>
       <c r="V25" t="n">
         <v>1.1089</v>
@@ -2419,7 +2419,7 @@
         <v>6.7603</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.6514</v>
+        <v>-5.651400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484278_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484278_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1016,6 +1046,11 @@
       </c>
       <c r="X7" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.5423</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.227</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1545,12 @@
       <c r="X13" t="n">
         <v>-6.760299999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1883</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>0.478</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2897</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9885</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2149</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2264</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3246</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3633</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3131</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8516</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5385</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1905</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2606</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2221</v>
+        <v>0.1883</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3706</v>
+        <v>0.478</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1485</v>
+        <v>-0.2897</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7017</v>
+        <v>-0.9885</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1228</v>
+        <v>-2.2149</v>
       </c>
       <c r="I15" t="n">
-        <v>0.579</v>
+        <v>1.2264</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0663</v>
+        <v>0.3246</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0258</v>
+        <v>-0.3633</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>0.6879</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3645</v>
+        <v>-1.3131</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.903</v>
+        <v>-1.8516</v>
       </c>
       <c r="O15" t="n">
         <v>0.5385</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0529</v>
+        <v>-0.1905</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4835</v>
+        <v>-0.2606</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5364</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2602</v>
+        <v>-0.2221</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2201</v>
+        <v>-1.3706</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04</v>
+        <v>1.1485</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4273</v>
+        <v>0.7017</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1975</v>
+        <v>0.1228</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2298</v>
+        <v>0.579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1223</v>
+        <v>1.0663</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0819</v>
+        <v>1.0258</v>
       </c>
       <c r="L16" t="n">
         <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5496</v>
+        <v>-0.3645</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2793</v>
+        <v>-0.903</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2702</v>
+        <v>0.5385</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1417</v>
+        <v>0.0529</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3425</v>
+        <v>-0.4835</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2008</v>
+        <v>0.5364</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.2602</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6</v>
+        <v>-0.2201</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0128</v>
+        <v>-0.04</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2186</v>
+        <v>-0.4273</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9486</v>
+        <v>-0.1975</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.27</v>
+        <v>-0.2298</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3249</v>
+        <v>0.1223</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3492</v>
+        <v>0.0819</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8937</v>
+        <v>-0.5496</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2978</v>
+        <v>-0.2793</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>-0.2702</v>
       </c>
       <c r="P17" t="n">
         <v>0.586</v>
@@ -1780,28 +1856,33 @@
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0454</v>
+        <v>-0.1417</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2751</v>
+        <v>-0.3425</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3205</v>
+        <v>0.2008</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8182</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5064</v>
+        <v>-0.6</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3118</v>
+        <v>0.0128</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6288</v>
+        <v>-1.2186</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5743</v>
+        <v>-0.9486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0545</v>
+        <v>-0.27</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4698</v>
+        <v>-0.3249</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3888</v>
+        <v>0.3492</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0986</v>
+        <v>-0.8937</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.2978</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1354</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1548</v>
+        <v>0.0454</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1493</v>
+        <v>-0.2751</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0054</v>
+        <v>0.3205</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1977,72 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8309</v>
+        <v>-2.8182</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5643</v>
+        <v>-2.5064</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2666</v>
+        <v>-0.3118</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.2521</v>
+        <v>-0.6288</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0934</v>
+        <v>-0.5743</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1587</v>
+        <v>-0.0545</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3252</v>
+        <v>0.4698</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6511</v>
+        <v>0.3888</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9269</v>
+        <v>-1.0986</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4423</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4846</v>
+        <v>-0.1354</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4924</v>
+        <v>0.1548</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3946</v>
+        <v>0.1493</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0978</v>
+        <v>0.0054</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2031,11 +2122,16 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6562</v>
+        <v>-4.1379</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1671</v>
+        <v>-2.8713</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4891</v>
+        <v>-1.2666</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6431</v>
+        <v>-4.5591</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8918</v>
+        <v>-2.4004</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7513</v>
+        <v>-2.1587</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1905</v>
+        <v>-1.6322</v>
       </c>
       <c r="K21" t="n">
-        <v>0.211</v>
+        <v>-0.9581</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4015</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4526</v>
+        <v>-2.9269</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1028</v>
+        <v>-1.4423</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3498</v>
+        <v>-1.4846</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.745</v>
+        <v>-0.4924</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8716</v>
+        <v>-0.3946</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1267</v>
+        <v>-0.0978</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>1.1089</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2963</v>
+        <v>-4.6562</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1763</v>
+        <v>-3.1671</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.12</v>
+        <v>-1.4891</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5039</v>
+        <v>-3.6431</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3456</v>
+        <v>-0.8918</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1583</v>
+        <v>-2.7513</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2049</v>
+        <v>-1.1905</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1433</v>
+        <v>0.211</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>-1.4015</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.299</v>
+        <v>-2.4526</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4889</v>
+        <v>-1.1028</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8101</v>
+        <v>-1.3498</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9534</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1025</v>
+        <v>0.745</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5371</v>
+        <v>0.8716</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6395999999999999</v>
+        <v>-0.1267</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6275</v>
+        <v>-5.2963</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.677</v>
+        <v>-3.1763</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9505</v>
+        <v>-2.12</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.7124</v>
+        <v>-2.5039</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6956</v>
+        <v>-0.3456</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.0168</v>
+        <v>-2.1583</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.031</v>
+        <v>-1.2049</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8262</v>
+        <v>0.1433</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.8573</v>
+        <v>-1.3482</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.6813</v>
+        <v>-1.299</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5219</v>
+        <v>-0.4889</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1595</v>
+        <v>-0.8101</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.0556</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8.009</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0977</v>
+        <v>0.1025</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2928</v>
+        <v>-0.5371</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3905</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>4.0428</v>
+        <v>-0.9414</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6559</v>
+        <v>1.4959</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3869</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.6906</v>
+        <v>-7.6275</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8194</v>
+        <v>-6.677</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8713</v>
+        <v>-0.9505</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.4759</v>
+        <v>-5.7124</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6833</v>
+        <v>-0.6956</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7925</v>
+        <v>-5.0168</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8795</v>
+        <v>-2.031</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2459</v>
+        <v>0.8262</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.8573</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.5964</v>
+        <v>-3.6813</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4375</v>
+        <v>-1.5219</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1589</v>
+        <v>-2.1595</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.586</v>
+        <v>-6.0556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-8.009</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1954</v>
+        <v>0.0977</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5958</v>
+        <v>-0.2928</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4004</v>
+        <v>0.3905</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8242</v>
+        <v>4.0428</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869</v>
+        <v>3.6559</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4373</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-8.6906</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.8194</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-4.8713</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.4759</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.6833</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.7925</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.8795</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.2459</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.5964</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.4375</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.1589</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.4004</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.8242</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484278_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-37.8688</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-26.7736</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-11.0953</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-26.3494</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>-10.834</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-15.5152</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>-6.5448</v>
       </c>
-      <c r="K25" t="n">
-        <v>0.8682000000000001</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K26" t="n">
+        <v>0.8682000000000005</v>
+      </c>
+      <c r="L26" t="n">
         <v>-7.413100000000001</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-19.8044</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-11.7025</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-8.102</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>-13.6739</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-26.3711</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>12.6971</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>1.0458</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-0.6179</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1.6634</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>1.1089</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>6.7603</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-5.651400000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
